--- a/data/trans_camb/IQ2608_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>27,74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>23,58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,67</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,13</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,0</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,22</t>
+          <t>12,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 37,08</t>
+          <t>14,17; 32,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 32,85</t>
+          <t>21,57; 37,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 21,74</t>
+          <t>0,98; 29,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,77; 32,27</t>
+          <t>18,86; 36,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 38,67</t>
+          <t>14,72; 32,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 29,89</t>
+          <t>-10,57; 21,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 31,67</t>
+          <t>19,48; 30,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 32,73</t>
+          <t>20,66; 32,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 22,6</t>
+          <t>-0,47; 22,02</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>50,19%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>42,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,38; 76,41</t>
+          <t>22,06; 59,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 67,48</t>
+          <t>33,48; 70,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 42,03</t>
+          <t>1,53; 52,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 61,22</t>
+          <t>31,05; 75,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,24; 72,23</t>
+          <t>24,96; 66,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 55,14</t>
+          <t>-17,81; 40,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 59,37</t>
+          <t>31,84; 57,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 61,37</t>
+          <t>33,94; 61,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 41,78</t>
+          <t>-0,67; 40,42</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,38</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25,82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>25,1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,38</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,56</t>
+          <t>19,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,13</t>
+          <t>18,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,0; 32,67</t>
+          <t>16,83; 30,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 32,15</t>
+          <t>13,55; 27,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 31,05</t>
+          <t>6,25; 27,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 29,61</t>
+          <t>18,7; 33,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,48</t>
+          <t>18,12; 32,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 28,39</t>
+          <t>4,64; 31,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,28; 28,88</t>
+          <t>19,84; 28,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,27; 27,49</t>
+          <t>17,74; 27,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 27,16</t>
+          <t>10,73; 26,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>45,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>44,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,48; 62,97</t>
+          <t>25,48; 52,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,86; 62,95</t>
+          <t>20,86; 48,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 58,46</t>
+          <t>9,36; 45,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 52,28</t>
+          <t>30,32; 65,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 45,92</t>
+          <t>29,33; 63,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 48,76</t>
+          <t>8,86; 58,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 51,55</t>
+          <t>31,72; 51,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 48,85</t>
+          <t>28,71; 48,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 47,7</t>
+          <t>17,45; 47,28</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,57</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>13,95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>28,12</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,75</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,65</t>
+          <t>-8,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>-8,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 22,41</t>
+          <t>4,41; 21,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,55; 35,98</t>
+          <t>14,49; 30,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 14,85</t>
+          <t>-24,4; 6,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 21,44</t>
+          <t>5,47; 22,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 30,77</t>
+          <t>19,54; 35,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 7,24</t>
+          <t>-26,26; 6,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 19,59</t>
+          <t>7,05; 19,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 30,64</t>
+          <t>20,15; 31,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 6,21</t>
+          <t>-20,0; 3,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-13,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>45,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-5,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,67%</t>
+          <t>-13,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,12%</t>
+          <t>-13,2%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 40,0</t>
+          <t>6,6; 36,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,78; 64,71</t>
+          <t>21,11; 52,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 25,31</t>
+          <t>-37,05; 10,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 36,85</t>
+          <t>8,25; 39,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,75; 53,45</t>
+          <t>28,85; 63,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 11,15</t>
+          <t>-40,48; 10,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 32,92</t>
+          <t>10,62; 34,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,35; 51,84</t>
+          <t>30,23; 52,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 10,68</t>
+          <t>-31,99; 5,87</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,88</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>14,69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,05</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 22,34</t>
+          <t>7,03; 21,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 14,12</t>
+          <t>2,55; 16,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 8,13</t>
+          <t>-22,76; 5,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 20,72</t>
+          <t>6,7; 21,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 16,55</t>
+          <t>-2,01; 13,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 6,55</t>
+          <t>-20,94; 5,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,07; 19,0</t>
+          <t>9,18; 19,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 12,85</t>
+          <t>2,44; 13,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 4,27</t>
+          <t>-17,33; 1,62</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-11,5%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>9,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-6,44%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,67%</t>
+          <t>-9,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,09%</t>
+          <t>-10,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 35,08</t>
+          <t>10,1; 33,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 22,28</t>
+          <t>3,58; 26,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 12,45</t>
+          <t>-32,66; 8,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 31,99</t>
+          <t>9,37; 34,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 25,57</t>
+          <t>-2,83; 22,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 9,84</t>
+          <t>-30,26; 9,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,69; 29,32</t>
+          <t>13,16; 30,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 20,01</t>
+          <t>3,38; 20,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 6,43</t>
+          <t>-24,97; 2,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19,69</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>20,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>19,93</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,97</t>
+          <t>14,55; 22,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,11</t>
+          <t>15,67; 23,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 11,7</t>
+          <t>-2,29; 11,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,03</t>
+          <t>16,15; 23,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,27</t>
+          <t>15,95; 23,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 12,23</t>
+          <t>-3,81; 10,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,67; 22,41</t>
+          <t>16,68; 21,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,72</t>
+          <t>17,17; 22,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,35</t>
+          <t>-1,22; 9,35</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33,48%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25,38; 41,84</t>
+          <t>22,02; 36,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25,82; 41,67</t>
+          <t>23,93; 38,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 19,49</t>
+          <t>-3,5; 18,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,16; 36,21</t>
+          <t>25,8; 40,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,99; 37,97</t>
+          <t>25,25; 40,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 19,44</t>
+          <t>-6,19; 17,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,15; 37,19</t>
+          <t>26,2; 36,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,21; 37,53</t>
+          <t>26,9; 37,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,72; 16,86</t>
+          <t>-1,93; 15,51</t>
         </is>
       </c>
     </row>
